--- a/KAMCHATKA_ITOG_2910.xlsx
+++ b/KAMCHATKA_ITOG_2910.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Что осталось" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По поставщикам КП" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все 315 позиций" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дороже бюджета (КП есть)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все 315 позиций" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Все 315 позиций'!$A$1:$L$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Все 315 позиций'!$A$1:$L$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,13 +544,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
@@ -721,188 +722,186 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Прибыль после УСН (с заморозкой денег 120 дн.)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
+          <t>А: дорогие позиции — на заводы по нашей цене</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Б: всё по КП, включая дорогие (+60 поз. по цене ДН.РУ/Тулы)</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>101102908</v>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Себестоимость лота</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>36987787.16682055</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+        <v>53275963.93</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>61108093.26</v>
+      </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>90992617.2</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>28462789.96426055</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Маржа при НМЦК</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>0.4730521111222636</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.3955852065105784</v>
+      </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>80882326.40000001</v>
+        <v>101102908</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19937792.76170055</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+        <v>36987787.16682055</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>29892736.30938356</v>
+      </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>70772035.59999999</v>
+        <v>90992617.2</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>11412795.55914054</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+        <v>28462789.96426055</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>21367739.10682356</v>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>60661744.8</v>
+        <v>80882326.40000001</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2887798.356580546</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+        <v>19937792.76170055</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>12842741.90426357</v>
+      </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+      <c r="A19" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>70772035.59999999</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>11412795.55914054</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>4317744.701703559</v>
+      </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>60661744.8</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2887798.356580546</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-4949708.824536988</v>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Статус позиции</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Позиций</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Сумма в себестоимости</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Наша цена</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Цена по КП</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Брать</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>12786095.61</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>14752521.11</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>12786095.61</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>КП</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Брать при условии</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>3324224.74</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>5499074.22</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>3324224.74</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>КП</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Торг: наш бюджет</t>
+          <t>Брать</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2478277.5</v>
+        <v>12786095.61</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2107692.36</v>
+        <v>14752521.11</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>2478277.5</v>
+        <v>12786095.61</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -913,66 +912,114 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Заказать у других</t>
+          <t>Брать при условии</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>5160042.9</v>
+        <v>3324224.74</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5733381</v>
+        <v>5499074.22</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>12992172.23</v>
+        <v>3324224.74</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>наша цена −10%</t>
+          <t>КП</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>Торг: наш бюджет</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2478277.5</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2107692.36</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2478277.5</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Заказать у других</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>5160042.9</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>5733381</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>12992172.23</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>наша цена −10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>Не отработано</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B27" s="10" t="n">
         <v>147</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="6" t="n">
         <v>26458299.18</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D27" s="6" t="n">
         <v>29398110.2</v>
       </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>наша цена −10%</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B28" s="13" t="n">
         <v>315</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C28" s="14" t="n">
         <v>50206939.93</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D28" s="14" t="n">
         <v>57490778.89</v>
       </c>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1300,6 +1347,1479 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Табл./№</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Позиция ТЗ</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Что в счёте</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Цена КП, ₽/шт</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Наша цена, ₽/шт</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Переплата, ₽</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Отклонение</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Альтернатива (завод с реестром)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>1.3/81</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 150 Ру 25</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду150 Ру25 фланцевая, корпус - сталь 25Л, материал 45-50 клин</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>137010.27</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>47645</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1694335.86</v>
+      </c>
+      <c r="I2" s="16" t="n">
+        <v>1.875648441599328</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +188%</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1.3/82</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 200 Ру 25</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду200 Ру25 фланцевая, корпус - сталь 25Л, материал 45-50 клин</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>216707.99</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>69188</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1389949.11</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>2.132161501994565</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +213%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1.3/84</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 300 Ру 25</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду300 Ру25 фланцевая, корпус - сталь 25Л, материал 45-50 клин</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>534704.04</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>158920</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1175028.12</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>2.364611376793355</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +236%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1.3/80</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 100 Ру 25</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду100 Ру25 фланцевая, корпус - сталь 25Л, материал 45-50 клин</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>75887.66</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>25064</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1066601.2</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>2.027755346313438</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +203%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.1/4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный15с52нж11 Ду 32 Ру 63 под приварку</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный сильфонный DN.ru VSO2236M-W-S Ду32 Ру63, приварной, корпус - углеродистая сталь A105, диск - м</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>76681.27</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>11059</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>800738.04</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>5.933833981372638</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +593%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Восточная арматурная компания»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1.3/83</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 250 Ру 25</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду250 Ру25 фланцевая, корпус - сталь 25Л, материал 45-50 клин</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>382612.13</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>100790</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>583802.26</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>2.796131858319278</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +280%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1.1/2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15нж65нж Ду 200 Ру 16</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задвижка клиновая 30нж15нж DN.ru GVWR3131M-2W-F-S Ду200 Ру40 фланцевая, с выдвижным шпинделем, корпус - сталь </t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>265092.58</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>520370.3200000001</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0.7672838666666668</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>другой товар (задвижка вместо клапана)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Восточная арматурная компания»</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>1.3/63</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15с52нж11 Ду 20 Ру 63 под приварку</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный сильфонный DN.ru VSO2236M-W-S Ду20 Ру63, приварной, корпус - углеродистая сталь A105, диск - м</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>44929.55</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>7956</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>226614.9</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>4.647253645047763</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +465%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Восточная арматурная компания»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>1.1/24</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Электропривод общепромышленный Н-В-02 У2</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Тулаэлектропривод</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Электропривод Н-В-02 У2 (250–630 Нм, 24 об/мин, 6–36 об. вых. вала, 3,2 кВт), ТУ 26-07-015-89, IP55, 380 В</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>203984</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>173968</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>0.5691076923076923</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +57%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>АО «Тулаэлектропривод»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>1.3/44</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Клапан мембранный запорный футерованный DN.ru VSO3434Flr-F Ду80 На складе в Ру16 фланцевый, корпус - углеродис</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>65515.22</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>19800</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>143085.66</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>2.308849494949495</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +231%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>1.3/79</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду80 Ру25 фланцевая, корпус - сталь 25Л, материал клина - 45-</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>53978.9</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>18390</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>112283.7</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>1.935231103860794</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +194%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>1.3/78</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду50 Ру25 фланцевая, корпус - сталь 25Л, материал клина - 45-</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>31275.92</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>10968</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>107023.6</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>1.851560904449307</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +185%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>1.3/41</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Клапан ВДХ Ду 80 Ру 10</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Клапан мембранный запорный футерованный DN.ru VSO3434Flr-F Ду80 На складе в Ру16 фланцевый, корпус - углеродис</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>65515.22</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>19800</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>95390.44</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>2.308849494949495</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +231%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>1.3/42</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Клапан мембранный запорный футерованный DN.ru VSO3434Flr-F Ду150 На складе в Ру16 фланцевый, корпус - углероди</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>181198.67</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>93000</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>97498.67000000001</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>0.948372795698925</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +95%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>1.5/3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду80 Ру25 фланцевая, корпус - сталь 25Л, материал клина - 45-</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>53978.9</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>18390</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>74855.8</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>1.935231103860794</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +194%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>1.3/95</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду100 Ру10 фланцевая, материал корпуса - чугун СЧ20, матери</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>11439.94</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>8410</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>73547.86000000002</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>0.3602782401902498</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +36%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПИК «АЛГРУПП»</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>1.7/1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>АРТ-85 Ду 50 Ру 16 "после себя"</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду50 Ру16 фланцевый, Kvy - 32м3/ч, Tmax 150°С, уплотне</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>89689.52</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>49189.52</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>0.9931004444444445</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +99%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Ридан»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>1.5/2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с64нж DN.ru GVWR2121M-2W-F-S Ду50 Ру25 фланцевая, корпус - сталь 25Л, материал клина - 45-</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>31275.92</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>10968</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>42809.44</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>1.851560904449307</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +185%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>1.3/43</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 50, Ру 16</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Клапан мембранный запорный футерованный DN.ru VSO3434Flr-F Ду50 На складе в Ру16 фланцевый, корпус - углеродис</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>40008.07</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>13400</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>27948.07</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>1.985676865671642</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +199%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>1.6/11</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный 17с11нж Ду 25 Ру 16</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный 17с11нж Ду25 Ру16 1 шт</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>30810.49</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>29220.98</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>0.7116938888888891</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +71%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» (бренд «Гранвэл»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1.3/67</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15ч93эм Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорно-регулирующий двухходовой DN.ru 25ч945п VSR1-11P- LED-F Ду20 Ру16 ETM односедельный, корпус – се</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>12024.93</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1668</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>21047.46</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>6.209190647482014</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +621%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>1.3/27</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Клапан обратный 19с76нж Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Клапан обратный ЧАЗ 19с76нж Ду80 Ру16 фланцевый, поворотный, корпус - углеродистая сталь 20Л/25Л, уплотнение -</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>33418.85</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>13503</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>21266.15</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>1.474920388061912</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +147%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (АО «БАЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>1.6/47</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду50 Ру16 фланцевая, материал корпуса - чугун СЧ20, материа</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>5247.22</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3705</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>17214.48</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>0.4162537112010798</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +42%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПИК «АЛГРУПП»</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>1.3/93</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду50 Ру16 фланцевая, материал корпуса - чугун СЧ20, материа</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>5247.22</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>3705</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>15301.76</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>0.4162537112010798</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +42%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПИК «АЛГРУПП»</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>1.6/49</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду100 Ру10 фланцевая, материал корпуса - чугун СЧ20, матери</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>11439.94</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>8410</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>11612.82</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>0.3602782401902498</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +36%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПИК «АЛГРУПП»</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>1.6/20</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15кч12пМ Ду 25 Ру 25</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный сальниковый DN.ru VSO2130M-F-S Ду25 Ру40, фланцевый, На складе в корпус - сталь GS-C25, уплотн</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>13534.07</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>8134.07</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>1.255678333333333</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>дороже нашей цены на +126%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (БАЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>1.3/19</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Клапан обратный двухстворчатый DENDOR 010C Ду 100 Ру 16</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клапан обратный Dendor 010C Ду100 Ру10 межфланцевый, двухстворчатый, корпус - чугун, диск - чугун, уплотнение </t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6150.02</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>7236</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-1811.900000000001</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>-0.1500801547816473</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>давление ниже ТЗ (Ру16 → Ру10)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>АО «Энергия» (производитель арматуры ДЕНДОР/DENDOR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>1.3/35</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Обратный клапан пружинный NVD-812R Ду 150 Ру 40</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клапан обратный DN.ru VCS3232-Fb Ду150 Ру25 ZGY межфланцевый, пружинный, корпус - нержавеющая сталь AISI 316, </t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>21604.98</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>195005</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-153899.52</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>-0.889208071587908</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>давление ниже ТЗ (Ру40 → Ру25)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Ридан»</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>1.1/11</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка 30С576НЖ Ду 300 Ру 63 с редуктором РК-Г-1М, в комплекте с крепежом и ответными фланцами.</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клиновая 30с541нж СибЗТА Ду300 Ру16 фланцевая, корпус - сталь 15 - 20 раб. WCB, с механическим редукт</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>188638.23</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>537930</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>-590997.54</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>-0.6493256929340249</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>давление ниже ТЗ (Ру63 → Ру16)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» (АО «БАЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="12" t="inlineStr"/>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>149</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr"/>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="14" t="n">
+        <v>12992172.23</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>5733381</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>7832129.33</v>
+      </c>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:L316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/KAMCHATKA_ITOG_2910.xlsx
+++ b/KAMCHATKA_ITOG_2910.xlsx
@@ -722,12 +722,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>А: дорогие позиции — на заводы по нашей цене</t>
+          <t>А: торг (31 поз.) по КП, 29 дорогих — на заводы по нашей цене</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Б: всё по КП, включая дорогие (+60 поз. по цене ДН.РУ/Тулы)</t>
+          <t>Б: всё по КП, включая 29 поз. «заказать у других» по цене ДН.РУ/Тулы</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
